--- a/artfynd/A 12403-2026 artfynd.xlsx
+++ b/artfynd/A 12403-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124313748</v>
+        <v>124313741</v>
       </c>
       <c r="B2" t="n">
-        <v>79795</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703376</v>
+        <v>703365</v>
       </c>
       <c r="R2" t="n">
-        <v>7094932</v>
+        <v>7094865</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124313744</v>
+        <v>124313743</v>
       </c>
       <c r="B3" t="n">
-        <v>79795</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703376</v>
+        <v>703368</v>
       </c>
       <c r="R3" t="n">
-        <v>7094869</v>
+        <v>7094884</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124313750</v>
+        <v>124313744</v>
       </c>
       <c r="B4" t="n">
-        <v>79795</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703456</v>
+        <v>703376</v>
       </c>
       <c r="R4" t="n">
-        <v>7094990</v>
+        <v>7094869</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,15 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124313749</v>
+        <v>124313746</v>
       </c>
       <c r="B5" t="n">
-        <v>79795</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703458</v>
+        <v>703380</v>
       </c>
       <c r="R5" t="n">
-        <v>7094964</v>
+        <v>7094895</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,15 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124313741</v>
+        <v>124313748</v>
       </c>
       <c r="B6" t="n">
-        <v>79795</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703365</v>
+        <v>703376</v>
       </c>
       <c r="R6" t="n">
-        <v>7094865</v>
+        <v>7094932</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,15 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124313746</v>
+        <v>124313749</v>
       </c>
       <c r="B7" t="n">
-        <v>79795</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>703380</v>
+        <v>703458</v>
       </c>
       <c r="R7" t="n">
-        <v>7094895</v>
+        <v>7094964</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,15 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124313743</v>
+        <v>124313750</v>
       </c>
       <c r="B8" t="n">
-        <v>79795</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>703368</v>
+        <v>703456</v>
       </c>
       <c r="R8" t="n">
-        <v>7094884</v>
+        <v>7094990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 12403-2026 artfynd.xlsx
+++ b/artfynd/A 12403-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124313741</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124313743</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124313744</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124313746</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124313748</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124313749</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,8 +1491,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124313750</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>